--- a/data/trans_dic/P16A04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,06</t>
+          <t>0,53; 2,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,69</t>
+          <t>2,32; 5,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,37</t>
+          <t>1,02; 3,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,23</t>
+          <t>1,06; 3,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,9</t>
+          <t>0,91; 3,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,45</t>
+          <t>1,79; 4,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,62</t>
+          <t>1,31; 3,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,29</t>
+          <t>1,66; 3,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,14</t>
+          <t>0,9; 2,1</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,52</t>
+          <t>2,36; 4,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,95</t>
+          <t>1,35; 2,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,92</t>
+          <t>1,6; 2,97</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,93</t>
+          <t>1,66; 4,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,59</t>
+          <t>2,01; 4,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,91</t>
+          <t>1,23; 2,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,88</t>
+          <t>0,8; 2,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,04</t>
+          <t>1,08; 3,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,71</t>
+          <t>2,99; 5,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,48</t>
+          <t>1,4; 3,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,15</t>
+          <t>2,3; 4,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,14</t>
+          <t>1,6; 3,02</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,67</t>
+          <t>2,81; 4,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,8</t>
+          <t>1,48; 2,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,11</t>
+          <t>1,51; 3,06</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,45</t>
+          <t>0,69; 2,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,36</t>
+          <t>1,77; 4,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,35</t>
+          <t>0,69; 2,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,18</t>
+          <t>1,41; 4,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 5,17</t>
+          <t>2,48; 5,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,54</t>
+          <t>0,7; 2,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,27</t>
+          <t>0,99; 3,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,57</t>
+          <t>1,18; 3,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,49</t>
+          <t>1,83; 3,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,1</t>
+          <t>1,41; 2,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,4</t>
+          <t>1,0; 2,41</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,38</t>
+          <t>1,52; 3,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,09; 2,8</t>
+          <t>1,11; 2,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,24</t>
+          <t>1,1; 3,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,19</t>
+          <t>1,97; 4,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,97</t>
+          <t>1,85; 3,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,89</t>
+          <t>1,17; 2,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,6</t>
+          <t>1,73; 3,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,89</t>
+          <t>1,68; 3,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,07</t>
+          <t>3,0; 5,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,46</t>
+          <t>1,34; 2,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,12</t>
+          <t>1,68; 3,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,59</t>
+          <t>2,02; 3,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 4,63</t>
+          <t>2,63; 4,42</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,28</t>
+          <t>1,38; 2,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,48</t>
+          <t>2,25; 3,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,59</t>
+          <t>1,57; 2,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,82</t>
+          <t>1,56; 2,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,77</t>
+          <t>1,75; 2,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,35; 3,52</t>
+          <t>2,28; 3,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,89</t>
+          <t>1,8; 2,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,73</t>
+          <t>2,49; 3,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,38</t>
+          <t>1,69; 2,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,29</t>
+          <t>2,43; 3,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,56</t>
+          <t>1,82; 2,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,08</t>
+          <t>2,17; 3,04</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antibióticos en las dos últimas semanas</t>
+          <t>Población que ha consumido antibióticos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3736; 14277</t>
+          <t>3672; 14167</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16270; 39908</t>
+          <t>16239; 39125</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6038; 22746</t>
+          <t>6887; 21665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6939; 20479</t>
+          <t>6757; 20416</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6428; 19957</t>
+          <t>6277; 20696</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12081; 30848</t>
+          <t>12410; 30979</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9227; 24330</t>
+          <t>8810; 23564</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11077; 22236</t>
+          <t>11212; 22315</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12011; 29541</t>
+          <t>12413; 29066</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33245; 63009</t>
+          <t>32917; 62798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19048; 39807</t>
+          <t>18126; 40190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20957; 38309</t>
+          <t>20950; 38978</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16074; 37762</t>
+          <t>16009; 38715</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21314; 46589</t>
+          <t>20419; 47129</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11911; 29746</t>
+          <t>12532; 29492</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9357; 34295</t>
+          <t>9525; 35074</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10771; 29419</t>
+          <t>10487; 29492</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31374; 58711</t>
+          <t>30742; 57864</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15622; 36301</t>
+          <t>14581; 34822</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22151; 39759</t>
+          <t>22010; 39668</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31364; 60544</t>
+          <t>30822; 58314</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57984; 95360</t>
+          <t>57396; 93399</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31774; 57923</t>
+          <t>30491; 56179</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32750; 66844</t>
+          <t>32375; 65782</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4649; 16599</t>
+          <t>4664; 16701</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12876; 32961</t>
+          <t>13371; 33128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4181; 17868</t>
+          <t>5211; 18725</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9737; 29391</t>
+          <t>9942; 29201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16061; 35361</t>
+          <t>16945; 36440</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5220; 19726</t>
+          <t>5434; 20342</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7951; 25642</t>
+          <t>7745; 25832</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9714; 33325</t>
+          <t>11037; 34673</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25757; 47479</t>
+          <t>24930; 47820</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22841; 47509</t>
+          <t>21587; 45841</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15695; 37007</t>
+          <t>15475; 37179</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25026; 55299</t>
+          <t>24954; 55135</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10268; 26402</t>
+          <t>10484; 26732</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10943; 30560</t>
+          <t>10400; 30162</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18368; 39288</t>
+          <t>18451; 39051</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16659; 36806</t>
+          <t>17127; 35974</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12048; 29981</t>
+          <t>12123; 30867</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17703; 37804</t>
+          <t>18157; 38348</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17982; 40609</t>
+          <t>17542; 40587</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31664; 66241</t>
+          <t>32794; 63766</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25453; 48673</t>
+          <t>26478; 50775</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32498; 62151</t>
+          <t>33403; 60870</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41446; 71202</t>
+          <t>39966; 70813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>54264; 93493</t>
+          <t>53089; 89238</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45782; 74568</t>
+          <t>45311; 75059</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>73191; 118752</t>
+          <t>76700; 118937</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53948; 87983</t>
+          <t>53214; 86710</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56889; 97638</t>
+          <t>54005; 97118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58066; 93580</t>
+          <t>59272; 93543</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83466; 124986</t>
+          <t>80717; 122792</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63427; 102289</t>
+          <t>63836; 101231</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>88403; 136558</t>
+          <t>91030; 136067</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112047; 158487</t>
+          <t>112191; 155307</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168636; 229140</t>
+          <t>168871; 228183</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>124314; 177422</t>
+          <t>126017; 177249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>157336; 219395</t>
+          <t>154438; 216564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A04-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P16A04-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,04</t>
+          <t>0,55; 2,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,58</t>
+          <t>2,33; 5,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,21</t>
+          <t>1,0; 3,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,22</t>
+          <t>1,08; 3,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,01</t>
+          <t>0,86; 2,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,47</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,5</t>
+          <t>1,29; 3,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,3</t>
+          <t>1,6; 3,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,1</t>
+          <t>0,89; 2,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,5</t>
+          <t>2,42; 4,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,98</t>
+          <t>1,37; 2,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,97</t>
+          <t>1,63; 2,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,03</t>
+          <t>1,63; 3,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,64</t>
+          <t>2,05; 4,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,88</t>
+          <t>1,26; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,94</t>
+          <t>1,41; 3,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,05</t>
+          <t>1,14; 3,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,63</t>
+          <t>3,08; 5,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,34</t>
+          <t>1,42; 3,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,14</t>
+          <t>2,1; 3,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,02</t>
+          <t>1,58; 2,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,57</t>
+          <t>2,89; 4,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,72</t>
+          <t>1,52; 2,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,06</t>
+          <t>1,97; 3,38</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,46</t>
+          <t>0,7; 2,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,38</t>
+          <t>1,76; 4,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,47</t>
+          <t>0,67; 2,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,15</t>
+          <t>1,47; 4,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,33</t>
+          <t>2,42; 5,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,62</t>
+          <t>0,74; 2,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,29</t>
+          <t>1,07; 3,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,72</t>
+          <t>2,43; 4,78</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,51</t>
+          <t>1,74; 3,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,99</t>
+          <t>1,45; 3,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,41</t>
+          <t>1,01; 2,38</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,37</t>
+          <t>2,2; 3,96</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1137,42 +1137,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,84</t>
+          <t>1,12; 2,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,2</t>
+          <t>1,04; 3,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,17</t>
+          <t>1,95; 4,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,88</t>
+          <t>1,66; 3,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,97</t>
+          <t>1,14; 2,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,66</t>
+          <t>1,76; 3,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,89</t>
+          <t>1,7; 3,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,84</t>
+          <t>3,31; 5,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,06</t>
+          <t>1,68; 3,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,57</t>
+          <t>2,02; 3,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,42</t>
+          <t>2,79; 4,22</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,29</t>
+          <t>1,4; 2,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,48</t>
+          <t>2,28; 3,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,55</t>
+          <t>1,6; 2,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,81</t>
+          <t>1,81; 2,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,77</t>
+          <t>1,7; 2,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,46</t>
+          <t>2,37; 3,51</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,86</t>
+          <t>1,79; 2,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,72</t>
+          <t>2,82; 3,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,33</t>
+          <t>1,69; 2,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,28</t>
+          <t>2,43; 3,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,55</t>
+          <t>1,83; 2,59</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,04</t>
+          <t>2,51; 3,26</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>17157</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>30784</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3672; 14167</t>
+          <t>3782; 14290</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16239; 39125</t>
+          <t>16296; 39031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6887; 21665</t>
+          <t>6728; 21064</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6757; 20416</t>
+          <t>7429; 24172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6277; 20696</t>
+          <t>5942; 19302</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12410; 30979</t>
+          <t>12898; 30547</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8810; 23564</t>
+          <t>8669; 23911</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11212; 22315</t>
+          <t>11689; 24387</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12413; 29066</t>
+          <t>12231; 29416</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32917; 62798</t>
+          <t>33748; 62742</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18126; 40190</t>
+          <t>18401; 39848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20950; 38978</t>
+          <t>23247; 42233</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>23341</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50150</t>
+          <t>54703</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16009; 38715</t>
+          <t>15640; 37195</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20419; 47129</t>
+          <t>20829; 46690</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12532; 29492</t>
+          <t>12865; 31532</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9525; 35074</t>
+          <t>14799; 37288</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10487; 29492</t>
+          <t>11024; 29634</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30742; 57864</t>
+          <t>31661; 60409</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14581; 34822</t>
+          <t>14787; 33927</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22010; 39668</t>
+          <t>22535; 41357</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30822; 58314</t>
+          <t>30427; 57454</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57396; 93399</t>
+          <t>59097; 95265</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30491; 56179</t>
+          <t>31423; 56949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32375; 65782</t>
+          <t>41693; 71678</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22006</t>
+          <t>28106</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39068</t>
+          <t>48176</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4664; 16701</t>
+          <t>4775; 16186</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13371; 33128</t>
+          <t>13347; 32414</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5211; 18725</t>
+          <t>5079; 19378</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9942; 29201</t>
+          <t>11792; 34261</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16945; 36440</t>
+          <t>16555; 36206</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5434; 20342</t>
+          <t>5765; 20622</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7745; 25832</t>
+          <t>8364; 29065</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11037; 34673</t>
+          <t>19756; 38809</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24930; 47820</t>
+          <t>23658; 47310</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21587; 45841</t>
+          <t>22245; 46472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15475; 37179</t>
+          <t>15573; 36688</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24954; 55135</t>
+          <t>35573; 63892</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24908</t>
+          <t>25109</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>44556</t>
+          <t>47518</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69465</t>
+          <t>72627</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10484; 26732</t>
+          <t>10585; 26573</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10400; 30162</t>
+          <t>9785; 28919</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18451; 39051</t>
+          <t>18291; 39266</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17127; 35974</t>
+          <t>16435; 36283</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12123; 30867</t>
+          <t>11854; 29153</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18157; 38348</t>
+          <t>18432; 38871</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17542; 40587</t>
+          <t>17694; 39220</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32794; 63766</t>
+          <t>36985; 61401</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26478; 50775</t>
+          <t>26513; 50662</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33403; 60870</t>
+          <t>33384; 60366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39966; 70813</t>
+          <t>40012; 70283</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>53089; 89238</t>
+          <t>58719; 88848</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75194</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>111657</t>
+          <t>124142</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>186852</t>
+          <t>206290</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45311; 75059</t>
+          <t>45808; 76703</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>76700; 118937</t>
+          <t>77743; 121968</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53214; 86710</t>
+          <t>54463; 88587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54005; 97118</t>
+          <t>64087; 104513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>59272; 93543</t>
+          <t>57529; 93713</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>80717; 122792</t>
+          <t>83879; 124616</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63836; 101231</t>
+          <t>63356; 101368</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>91030; 136067</t>
+          <t>105311; 144065</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>112191; 155307</t>
+          <t>112708; 159284</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>168871; 228183</t>
+          <t>168997; 230362</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126017; 177249</t>
+          <t>126736; 179493</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>154438; 216564</t>
+          <t>182214; 236764</t>
         </is>
       </c>
     </row>
